--- a/artfynd/A 44833-2024 artfynd.xlsx
+++ b/artfynd/A 44833-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121641293</v>
+        <v>121641244</v>
       </c>
       <c r="B2" t="n">
-        <v>82393</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704188</v>
+        <v>704122</v>
       </c>
       <c r="R2" t="n">
-        <v>7206806</v>
+        <v>7206974</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641276</v>
+        <v>121641293</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704016</v>
+        <v>704188</v>
       </c>
       <c r="R3" t="n">
-        <v>7206975</v>
+        <v>7206806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641269</v>
+        <v>121641266</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Råliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>704088</v>
+        <v>704262</v>
       </c>
       <c r="R4" t="n">
-        <v>7206976</v>
+        <v>7207047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121641266</v>
+        <v>121641269</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,42 +1009,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Råliden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>704262</v>
+        <v>704088</v>
       </c>
       <c r="R5" t="n">
-        <v>7207047</v>
+        <v>7206976</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121641244</v>
+        <v>121641253</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>98134</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>704122</v>
+        <v>704106</v>
       </c>
       <c r="R6" t="n">
-        <v>7206974</v>
+        <v>7206969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121641253</v>
+        <v>121641294</v>
       </c>
       <c r="B7" t="n">
-        <v>98126</v>
+        <v>82400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,25 +1221,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704106</v>
+        <v>704105</v>
       </c>
       <c r="R7" t="n">
-        <v>7206969</v>
+        <v>7206974</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121641294</v>
+        <v>121641276</v>
       </c>
       <c r="B8" t="n">
-        <v>82393</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704105</v>
+        <v>704016</v>
       </c>
       <c r="R8" t="n">
-        <v>7206974</v>
+        <v>7206975</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 44833-2024 artfynd.xlsx
+++ b/artfynd/A 44833-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641269</v>
+        <v>121641293</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704088</v>
+        <v>704188</v>
       </c>
       <c r="R3" t="n">
-        <v>7206976</v>
+        <v>7206806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641294</v>
+        <v>121641253</v>
       </c>
       <c r="B4" t="n">
-        <v>82400</v>
+        <v>98134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>704105</v>
+        <v>704106</v>
       </c>
       <c r="R4" t="n">
-        <v>7206974</v>
+        <v>7206969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121641244</v>
+        <v>121641269</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>704122</v>
+        <v>704088</v>
       </c>
       <c r="R5" t="n">
-        <v>7206974</v>
+        <v>7206976</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121641293</v>
+        <v>121641294</v>
       </c>
       <c r="B6" t="n">
         <v>82400</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>704188</v>
+        <v>704105</v>
       </c>
       <c r="R6" t="n">
-        <v>7206806</v>
+        <v>7206974</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121641253</v>
+        <v>121641244</v>
       </c>
       <c r="B7" t="n">
-        <v>98134</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,25 +1221,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704106</v>
+        <v>704122</v>
       </c>
       <c r="R7" t="n">
-        <v>7206969</v>
+        <v>7206974</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 44833-2024 artfynd.xlsx
+++ b/artfynd/A 44833-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121641266</v>
+        <v>121641294</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>82400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Råliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704262</v>
+        <v>704105</v>
       </c>
       <c r="R2" t="n">
-        <v>7207047</v>
+        <v>7206974</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641293</v>
+        <v>121641253</v>
       </c>
       <c r="B3" t="n">
-        <v>82400</v>
+        <v>98134</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704188</v>
+        <v>704106</v>
       </c>
       <c r="R3" t="n">
-        <v>7206806</v>
+        <v>7206969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641253</v>
+        <v>121641276</v>
       </c>
       <c r="B4" t="n">
-        <v>98134</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>704106</v>
+        <v>704016</v>
       </c>
       <c r="R4" t="n">
-        <v>7206969</v>
+        <v>7206975</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121641269</v>
+        <v>121641266</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,38 +1005,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Råliden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>704088</v>
+        <v>704262</v>
       </c>
       <c r="R5" t="n">
-        <v>7206976</v>
+        <v>7207047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121641294</v>
+        <v>121641269</v>
       </c>
       <c r="B6" t="n">
-        <v>82400</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>704105</v>
+        <v>704088</v>
       </c>
       <c r="R6" t="n">
-        <v>7206974</v>
+        <v>7206976</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121641244</v>
+        <v>121641293</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>82400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704122</v>
+        <v>704188</v>
       </c>
       <c r="R7" t="n">
-        <v>7206974</v>
+        <v>7206806</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121641276</v>
+        <v>121641244</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704016</v>
+        <v>704122</v>
       </c>
       <c r="R8" t="n">
-        <v>7206975</v>
+        <v>7206974</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
